--- a/morph/morph_clean.xlsx
+++ b/morph/morph_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevo\OneDrive\Documents\GitHub\TEdissy_analysis\morph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F72E89-AF83-4CEB-83BA-001663B4BA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB66C7E-D78C-4B4E-BFF7-067E71E0A3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{95908F03-C67E-4C74-9B43-83A62FD521B1}"/>
+    <workbookView xWindow="20" yWindow="0" windowWidth="19180" windowHeight="10180" xr2:uid="{95908F03-C67E-4C74-9B43-83A62FD521B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,26 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="142">
-  <si>
-    <t>R number</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Divisions</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="140">
   <si>
     <t>PhotoID</t>
   </si>
   <si>
-    <t>Blade width largest at widest point mm</t>
-  </si>
-  <si>
     <t>dry weight</t>
   </si>
   <si>
@@ -65,9 +50,6 @@
     <t>Concession</t>
   </si>
   <si>
-    <t>C.Cham</t>
-  </si>
-  <si>
     <t>Gam</t>
   </si>
   <si>
@@ -83,9 +65,6 @@
     <t>C. Cham</t>
   </si>
   <si>
-    <t>Ca</t>
-  </si>
-  <si>
     <t>I26</t>
   </si>
   <si>
@@ -462,6 +441,21 @@
   </si>
   <si>
     <t>Life_S</t>
+  </si>
+  <si>
+    <t>height_cm</t>
+  </si>
+  <si>
+    <t>bladewidth_mm</t>
+  </si>
+  <si>
+    <t>R_num</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>divisions</t>
   </si>
 </sst>
 </file>
@@ -842,42 +836,42 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>22.2</v>
@@ -886,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -900,13 +894,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>58</v>
@@ -915,10 +909,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -929,13 +923,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>12.5</v>
@@ -944,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -958,13 +952,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>38.700000000000003</v>
@@ -973,10 +967,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H5">
         <v>15</v>
@@ -987,13 +981,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>52.8</v>
@@ -1002,10 +996,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
         <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
       </c>
       <c r="H6">
         <v>16.5</v>
@@ -1016,13 +1010,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>37</v>
@@ -1031,10 +1025,10 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>14</v>
@@ -1045,13 +1039,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>36.1</v>
@@ -1060,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H8">
         <v>5.5</v>
@@ -1074,13 +1068,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>25</v>
@@ -1089,10 +1083,10 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -1103,13 +1097,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>25</v>
@@ -1118,10 +1112,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1132,13 +1126,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>26</v>
@@ -1147,10 +1141,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -1161,13 +1155,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>31.4</v>
@@ -1176,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -1190,13 +1184,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>26</v>
@@ -1205,10 +1199,10 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -1219,13 +1213,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>22.5</v>
@@ -1234,10 +1228,10 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1248,13 +1242,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>26</v>
@@ -1263,10 +1257,10 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H15">
         <v>11</v>
@@ -1277,13 +1271,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>22.6</v>
@@ -1292,10 +1286,10 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H16">
         <v>7</v>
@@ -1306,13 +1300,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>37</v>
@@ -1321,10 +1315,10 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H17">
         <v>8</v>
@@ -1335,13 +1329,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>21.2</v>
@@ -1350,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -1364,13 +1358,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>18.3</v>
@@ -1379,10 +1373,10 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1393,13 +1387,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>36.200000000000003</v>
@@ -1408,10 +1402,10 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H20">
         <v>11</v>
@@ -1422,13 +1416,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>22</v>
@@ -1437,10 +1431,10 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H21">
         <v>6.5</v>
@@ -1451,22 +1445,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>17.3</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H22">
         <v>7</v>
@@ -1477,13 +1471,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>20</v>
@@ -1492,10 +1486,10 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -1506,13 +1500,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>21.2</v>
@@ -1521,10 +1515,10 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -1535,13 +1529,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>21.7</v>
@@ -1550,10 +1544,10 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -1564,13 +1558,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>33.200000000000003</v>
@@ -1579,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H26">
         <v>7</v>
@@ -1593,13 +1587,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>26.2</v>
@@ -1608,10 +1602,10 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H27">
         <v>8</v>
@@ -1622,13 +1616,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>20.5</v>
@@ -1637,10 +1631,10 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H28">
         <v>9</v>
@@ -1651,13 +1645,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>20.5</v>
@@ -1666,10 +1660,10 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -1680,13 +1674,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>17.5</v>
@@ -1695,10 +1689,10 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -1709,13 +1703,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>21.5</v>
@@ -1724,10 +1718,10 @@
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H31">
         <v>8</v>
@@ -1738,13 +1732,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>23.5</v>
@@ -1753,10 +1747,10 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H32">
         <v>6</v>
@@ -1767,13 +1761,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>26.7</v>
@@ -1782,10 +1776,10 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H33">
         <v>9</v>
@@ -1796,13 +1790,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>24</v>
@@ -1811,10 +1805,10 @@
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H34">
         <v>14</v>
@@ -1825,13 +1819,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>24.7</v>
@@ -1840,10 +1834,10 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H35">
         <v>6</v>
@@ -1854,13 +1848,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
         <v>27</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>34</v>
-      </c>
-      <c r="C36" t="s">
-        <v>41</v>
       </c>
       <c r="D36">
         <v>12</v>
@@ -1869,10 +1863,10 @@
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -1883,13 +1877,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
         <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
       </c>
       <c r="D37">
         <v>11.6</v>
@@ -1898,10 +1892,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -1912,13 +1906,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>24.5</v>
@@ -1927,10 +1921,10 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H38">
         <v>6</v>
@@ -1941,13 +1935,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>18.2</v>
@@ -1956,10 +1950,10 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H39">
         <v>10</v>
@@ -1970,13 +1964,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
         <v>34</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
       </c>
       <c r="D40">
         <v>13.5</v>
@@ -1985,10 +1979,10 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -1999,13 +1993,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>26.6</v>
@@ -2014,10 +2008,10 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H41">
         <v>7</v>
@@ -2028,13 +2022,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
         <v>34</v>
-      </c>
-      <c r="C42" t="s">
-        <v>41</v>
       </c>
       <c r="D42">
         <v>10.5</v>
@@ -2043,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H42">
         <v>4</v>
@@ -2057,13 +2051,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>18</v>
@@ -2072,10 +2066,10 @@
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H43">
         <v>7</v>
@@ -2086,13 +2080,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
         <v>34</v>
-      </c>
-      <c r="C44" t="s">
-        <v>41</v>
       </c>
       <c r="D44">
         <v>12.6</v>
@@ -2101,10 +2095,10 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H44">
         <v>6</v>
@@ -2115,13 +2109,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>12</v>
@@ -2130,10 +2124,10 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H45">
         <v>2.5</v>
@@ -2144,13 +2138,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>23</v>
@@ -2159,10 +2153,10 @@
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H46">
         <v>11</v>
@@ -2173,13 +2167,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D47">
         <v>25.6</v>
@@ -2188,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H47">
         <v>8</v>
@@ -2202,13 +2196,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48">
         <v>20.9</v>
@@ -2217,10 +2211,10 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G48" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -2231,13 +2225,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>23</v>
@@ -2246,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -2260,13 +2254,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
         <v>27</v>
       </c>
-      <c r="B50" t="s">
-        <v>34</v>
-      </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50">
         <v>24.4</v>
@@ -2275,10 +2269,10 @@
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H50">
         <v>6</v>
@@ -2289,13 +2283,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>24.9</v>
@@ -2304,10 +2298,10 @@
         <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G51" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H51">
         <v>10.5</v>
@@ -2318,13 +2312,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>23.1</v>
@@ -2333,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G52" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -2347,13 +2341,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>17</v>
@@ -2362,10 +2356,10 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H53">
         <v>3</v>
@@ -2376,13 +2370,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54">
         <v>23.7</v>
@@ -2391,10 +2385,10 @@
         <v>4</v>
       </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -2405,13 +2399,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>23.4</v>
@@ -2420,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H55">
         <v>9</v>
@@ -2434,13 +2428,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56">
         <v>27.8</v>
@@ -2449,10 +2443,10 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H56">
         <v>3.5</v>
@@ -2463,13 +2457,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" t="s">
         <v>27</v>
       </c>
-      <c r="B57" t="s">
-        <v>34</v>
-      </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57">
         <v>21.7</v>
@@ -2478,10 +2472,10 @@
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H57">
         <v>6</v>
@@ -2492,13 +2486,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58">
         <v>19.899999999999999</v>
@@ -2507,10 +2501,10 @@
         <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H58">
         <v>8</v>
@@ -2521,13 +2515,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>14.1</v>
@@ -2536,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H59">
         <v>9</v>
@@ -2550,13 +2544,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60">
         <v>16.899999999999999</v>
@@ -2565,10 +2559,10 @@
         <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G60" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H60">
         <v>2.5</v>
@@ -2579,13 +2573,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D61">
         <v>19.2</v>
@@ -2594,10 +2588,10 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H61">
         <v>7</v>
@@ -2608,13 +2602,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" t="s">
         <v>27</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>34</v>
-      </c>
-      <c r="C62" t="s">
-        <v>41</v>
       </c>
       <c r="D62">
         <v>9.5</v>
@@ -2623,10 +2617,10 @@
         <v>2</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H62">
         <v>3.5</v>
@@ -2637,13 +2631,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D63">
         <v>11.5</v>
@@ -2652,10 +2646,10 @@
         <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G63" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H63">
         <v>4</v>
@@ -2666,22 +2660,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" t="s">
         <v>27</v>
       </c>
-      <c r="B64" t="s">
-        <v>34</v>
-      </c>
       <c r="C64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>22.1</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -2692,13 +2686,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <v>21.8</v>
@@ -2707,10 +2701,10 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H65">
         <v>7</v>
@@ -2721,13 +2715,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>23.6</v>
@@ -2736,10 +2730,10 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H66">
         <v>3.5</v>
@@ -2750,13 +2744,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" t="s">
         <v>34</v>
-      </c>
-      <c r="C67" t="s">
-        <v>41</v>
       </c>
       <c r="D67">
         <v>8.1999999999999993</v>
@@ -2765,10 +2759,10 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H67">
         <v>3.5</v>
@@ -2779,13 +2773,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <v>17</v>
@@ -2794,10 +2788,10 @@
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H68">
         <v>5.5</v>
@@ -2808,13 +2802,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69">
         <v>20.5</v>
@@ -2823,10 +2817,10 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2837,13 +2831,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
         <v>34</v>
-      </c>
-      <c r="C70" t="s">
-        <v>41</v>
       </c>
       <c r="D70">
         <v>11.3</v>
@@ -2852,10 +2846,10 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2866,13 +2860,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71">
         <v>23.3</v>
@@ -2881,10 +2875,10 @@
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G71" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -2895,13 +2889,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="s">
         <v>34</v>
-      </c>
-      <c r="C72" t="s">
-        <v>41</v>
       </c>
       <c r="D72">
         <v>12.2</v>
@@ -2910,10 +2904,10 @@
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H72">
         <v>4</v>
@@ -2924,13 +2918,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D73">
         <v>18.3</v>
@@ -2939,10 +2933,10 @@
         <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -2953,13 +2947,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D74">
         <v>12.5</v>
@@ -2968,10 +2962,10 @@
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G74" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H74">
         <v>6</v>
@@ -2982,13 +2976,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" t="s">
         <v>34</v>
-      </c>
-      <c r="C75" t="s">
-        <v>41</v>
       </c>
       <c r="D75">
         <v>10.5</v>
@@ -2997,10 +2991,10 @@
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G75" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H75">
         <v>6</v>
@@ -3011,13 +3005,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D76">
         <v>25.5</v>
@@ -3026,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G76" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H76">
         <v>9</v>
@@ -3040,13 +3034,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D77">
         <v>20.8</v>
@@ -3055,10 +3049,10 @@
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H77">
         <v>7</v>
@@ -3069,13 +3063,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" t="s">
         <v>34</v>
-      </c>
-      <c r="C78" t="s">
-        <v>41</v>
       </c>
       <c r="D78">
         <v>11</v>
@@ -3084,10 +3078,10 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H78">
         <v>4</v>
@@ -3098,13 +3092,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D79">
         <v>16</v>
@@ -3113,10 +3107,10 @@
         <v>2</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G79" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -3127,13 +3121,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D80">
         <v>18.600000000000001</v>
@@ -3142,10 +3136,10 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G80" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H80">
         <v>2.5</v>
@@ -3156,13 +3150,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D81">
         <v>16.3</v>
@@ -3171,10 +3165,10 @@
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H81">
         <v>7</v>
@@ -3185,13 +3179,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D82">
         <v>13.4</v>
@@ -3200,10 +3194,10 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H82">
         <v>4</v>
@@ -3214,13 +3208,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" t="s">
         <v>34</v>
-      </c>
-      <c r="C83" t="s">
-        <v>41</v>
       </c>
       <c r="D83">
         <v>10</v>
@@ -3229,10 +3223,10 @@
         <v>5</v>
       </c>
       <c r="F83" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H83">
         <v>4</v>
@@ -3243,13 +3237,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D84">
         <v>18</v>
@@ -3258,10 +3252,10 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -3272,13 +3266,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B85" t="s">
         <v>27</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>34</v>
-      </c>
-      <c r="C85" t="s">
-        <v>41</v>
       </c>
       <c r="D85">
         <v>11.7</v>
@@ -3287,10 +3281,10 @@
         <v>4</v>
       </c>
       <c r="F85" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H85">
         <v>4</v>
@@ -3301,13 +3295,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86">
         <v>17.8</v>
@@ -3316,10 +3310,10 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G86" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -3330,13 +3324,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" t="s">
         <v>27</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>34</v>
-      </c>
-      <c r="C87" t="s">
-        <v>41</v>
       </c>
       <c r="D87">
         <v>10.5</v>
@@ -3345,10 +3339,10 @@
         <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G87" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H87">
         <v>4</v>
@@ -3359,13 +3353,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" t="s">
         <v>27</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>34</v>
-      </c>
-      <c r="C88" t="s">
-        <v>41</v>
       </c>
       <c r="D88">
         <v>13</v>
@@ -3374,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G88" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H88">
         <v>5</v>
@@ -3388,13 +3382,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D89">
         <v>9.6</v>
@@ -3403,10 +3397,10 @@
         <v>4</v>
       </c>
       <c r="F89" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -3417,13 +3411,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D90">
         <v>11.5</v>
@@ -3432,10 +3426,10 @@
         <v>4</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G90" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H90">
         <v>4</v>
@@ -3446,13 +3440,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D91">
         <v>12.6</v>
@@ -3461,10 +3455,10 @@
         <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G91" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H91">
         <v>3.5</v>
@@ -3475,13 +3469,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D92">
         <v>10</v>
@@ -3490,10 +3484,10 @@
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H92">
         <v>3.5</v>
@@ -3504,13 +3498,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>21.1</v>
@@ -3519,10 +3513,10 @@
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G93" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H93">
         <v>5</v>
@@ -3533,13 +3527,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D94">
         <v>20.100000000000001</v>
@@ -3548,10 +3542,10 @@
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H94">
         <v>5</v>
@@ -3562,13 +3556,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D95">
         <v>19</v>
@@ -3577,10 +3571,10 @@
         <v>4</v>
       </c>
       <c r="F95" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H95">
         <v>7</v>
@@ -3591,13 +3585,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D96">
         <v>10.5</v>
@@ -3606,10 +3600,10 @@
         <v>6</v>
       </c>
       <c r="F96" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H96">
         <v>3.5</v>
@@ -3620,13 +3614,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D97">
         <v>21.6</v>
@@ -3635,10 +3629,10 @@
         <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H97">
         <v>5</v>
@@ -3649,13 +3643,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>21.7</v>
@@ -3664,10 +3658,10 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H98">
         <v>5.5</v>
@@ -3678,22 +3672,22 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" t="s">
         <v>27</v>
       </c>
-      <c r="B99" t="s">
-        <v>34</v>
-      </c>
       <c r="C99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D99">
         <v>14.3</v>
       </c>
       <c r="F99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H99">
         <v>6</v>
@@ -3704,13 +3698,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D100">
         <v>9</v>
@@ -3719,10 +3713,10 @@
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H100">
         <v>2</v>
@@ -3733,13 +3727,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D101">
         <v>13.6</v>
@@ -3748,10 +3742,10 @@
         <v>5</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H101">
         <v>7</v>
@@ -3762,13 +3756,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D102">
         <v>16</v>
@@ -3777,10 +3771,10 @@
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H102">
         <v>4.5</v>
@@ -3791,13 +3785,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D103">
         <v>12</v>
@@ -3806,10 +3800,10 @@
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G103" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H103">
         <v>4</v>
@@ -3820,13 +3814,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D104">
         <v>12</v>
@@ -3835,10 +3829,10 @@
         <v>4</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H104">
         <v>6.5</v>
@@ -3849,13 +3843,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
+        <v>27</v>
+      </c>
+      <c r="C105" t="s">
         <v>34</v>
-      </c>
-      <c r="C105" t="s">
-        <v>41</v>
       </c>
       <c r="D105">
         <v>11</v>
@@ -3864,10 +3858,10 @@
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H105">
         <v>5</v>
@@ -3878,13 +3872,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D106">
         <v>13.4</v>
@@ -3893,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H106">
         <v>7.5</v>
@@ -3907,13 +3901,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D107">
         <v>8.3000000000000007</v>
@@ -3922,10 +3916,10 @@
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G107" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H107">
         <v>4</v>
@@ -3936,13 +3930,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" t="s">
         <v>34</v>
-      </c>
-      <c r="C108" t="s">
-        <v>41</v>
       </c>
       <c r="D108">
         <v>15.1</v>
@@ -3951,10 +3945,10 @@
         <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H108">
         <v>4</v>
@@ -3965,13 +3959,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" t="s">
         <v>34</v>
-      </c>
-      <c r="C109" t="s">
-        <v>41</v>
       </c>
       <c r="D109">
         <v>11.3</v>
@@ -3980,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H109">
         <v>4</v>
@@ -3994,13 +3988,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D110">
         <v>7</v>
@@ -4009,10 +4003,10 @@
         <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H110">
         <v>3</v>
@@ -4023,13 +4017,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D111">
         <v>11.1</v>
@@ -4038,10 +4032,10 @@
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H111">
         <v>7</v>
@@ -4052,13 +4046,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D112">
         <v>10</v>
@@ -4067,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G112" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H112">
         <v>3</v>
@@ -4081,13 +4075,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D113">
         <v>17.8</v>
@@ -4096,10 +4090,10 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="H113">
         <v>4</v>
@@ -4110,13 +4104,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D114">
         <v>7.9</v>
@@ -4125,10 +4119,10 @@
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G114" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H114">
         <v>3</v>
@@ -4139,13 +4133,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D115">
         <v>10.1</v>
@@ -4154,10 +4148,10 @@
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G115" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H115">
         <v>4</v>
@@ -4168,13 +4162,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B116" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" t="s">
         <v>34</v>
-      </c>
-      <c r="C116" t="s">
-        <v>41</v>
       </c>
       <c r="D116">
         <v>7.5</v>
@@ -4183,10 +4177,10 @@
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -4197,13 +4191,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D117">
         <v>8</v>
@@ -4212,10 +4206,10 @@
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G117" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H117">
         <v>4.5</v>
@@ -4226,13 +4220,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" t="s">
         <v>34</v>
-      </c>
-      <c r="C118" t="s">
-        <v>41</v>
       </c>
       <c r="D118">
         <v>12.7</v>
@@ -4241,10 +4235,10 @@
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G118" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H118">
         <v>6</v>
@@ -4259,6 +4253,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A67FDF095F6D1D45AAE334723985296E" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="836cafe6d8d7281e8b54aa1057464286">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3fc1142c-e1d8-4a93-a6a4-19c12bdcfc0c" xmlns:ns4="7a3c1b20-21d9-4319-9926-2b72ce2d98ed" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a15d1b057bc7c5b4a844940d13deb846" ns3:_="" ns4:_="">
     <xsd:import namespace="3fc1142c-e1d8-4a93-a6a4-19c12bdcfc0c"/>
@@ -4505,15 +4508,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4523,6 +4517,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128E9EF-2680-4004-A4B8-63C24B46217C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBA9226-EFF6-4C95-9E5A-E831334C63EC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4537,14 +4539,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5128E9EF-2680-4004-A4B8-63C24B46217C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
